--- a/output/pdf_financials_xlsx/ADEN.xlsx
+++ b/output/pdf_financials_xlsx/ADEN.xlsx
@@ -2469,28 +2469,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.392</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.766</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.313</v>
@@ -2583,28 +2583,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.392</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.766</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.313</v>
@@ -3267,28 +3267,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.627</v>
+        <v>3.164</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.294</v>
+        <v>0.902</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.117</v>
+        <v>1.023</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.283</v>
+        <v>1.205</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.964</v>
+        <v>1.951</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.193</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.426</v>
+        <v>4.66</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>7.163</v>
+        <v>6.85</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>6.85</v>
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-19.572</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-57.041</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -7808,10 +7808,10 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-19.572</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-57.041</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -20160,7 +20160,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -23506,7 +23506,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
@@ -33206,7 +33206,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ADEN.xlsx
+++ b/output/pdf_financials_xlsx/ADEN.xlsx
@@ -1108,43 +1108,43 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>1.028</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>0.569</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.753</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.178</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.381</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>1.465</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>2.502</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>7.979</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>5.661</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>10.68</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>33.862</v>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
@@ -2086,31 +2086,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.881</v>
+        <v>1.853</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9.644</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16.097</v>
+        <v>15.344</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>31.881</v>
+        <v>31.703</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>36.056</v>
+        <v>35.675</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>51.024</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>60.946</v>
+        <v>59.481</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>76.021</v>
+        <v>73.51900000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>71.355</v>
+        <v>63.376</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2118,13 +2118,13 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>141.135</v>
+        <v>135.474</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>137.651</v>
+        <v>126.971</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>162.77</v>
+        <v>128.908</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -2210,31 +2210,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4.019</v>
+        <v>2.991</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10.646</v>
+        <v>10.077</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>17.363</v>
+        <v>16.61</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>33.323</v>
+        <v>33.145</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>38.194</v>
+        <v>37.813</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>53.617</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>65.752</v>
+        <v>64.28700000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>82.52500000000001</v>
+        <v>80.023</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>96.892</v>
+        <v>88.913</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>164.418</v>
+        <v>158.757</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>174.23</v>
+        <v>163.55</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>228.225</v>
+        <v>194.363</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2273,31 +2273,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.033340922314133</v>
+        <v>1.513242771495788</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.628313313248036</v>
+        <v>4.38094244388507</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.672570216964458</v>
+        <v>5.426561729181572</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8.976738547741874</v>
+        <v>8.928787899195884</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>8.381501621702283</v>
+        <v>8.297892884260051</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>9.380193772546439</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8.33019772690705</v>
+        <v>8.144595164704855</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>7.890786353553125</v>
+        <v>7.651552818786812</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>8.542256805496413</v>
+        <v>7.838806912305481</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>17.70909850738552</v>
+        <v>17.09936473948718</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.7802318897611</v>
+        <v>10.11942217511581</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.847411659626728</v>
+        <v>7.534711238470939</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -6985,43 +6985,43 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.453</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.771</v>
       </c>
       <c r="O112" s="1" t="inlineStr">
         <is>
@@ -31798,7 +31798,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -35418,7 +35422,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E288" s="5" t="n">
         <v>0.22</v>
       </c>
@@ -39020,7 +39028,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -44896,7 +44908,11 @@
           <t>Net finance expense 16</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -50528,7 +50544,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -58430,7 +58450,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E534" s="5" t="n">
         <v>-1.028</v>
       </c>

--- a/output/pdf_financials_xlsx/ADEN.xlsx
+++ b/output/pdf_financials_xlsx/ADEN.xlsx
@@ -5046,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>137.324</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>173.225</v>
       </c>
       <c r="Q78" s="1" t="inlineStr">
         <is>
@@ -5103,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>137.324</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>0</v>
+        <v>173.225</v>
       </c>
       <c r="Q79" s="1" t="inlineStr">
         <is>
@@ -5185,15 +5185,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O80" s="3" t="n">
+        <v>0.2606426289746748</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.2729792679160127</v>
       </c>
       <c r="Q80" s="1" t="inlineStr">
         <is>
@@ -5475,10 +5471,10 @@
         <v>488.574</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>477.526</v>
+        <v>340.202</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>484.739</v>
+        <v>311.514</v>
       </c>
       <c r="Q85" s="1" t="inlineStr">
         <is>
@@ -6692,31 +6688,31 @@
         <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>1.299</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>3.287</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>2.096</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>2.249</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>2.647</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>5.537</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>3.899</v>
       </c>
       <c r="O107" s="1" t="inlineStr">
         <is>
@@ -7561,16 +7557,16 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-3.443</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="M121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-27.135</v>
       </c>
       <c r="O121" s="1" t="inlineStr">
         <is>
@@ -10964,7 +10960,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -30060,7 +30060,11 @@
           <t>Share-based compensation expense 14(b)</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -31418,7 +31422,11 @@
           <t>Repurchase of common shares 14(a)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -34444,7 +34452,11 @@
           <t>Share-based compensation expense 13(b)</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -35052,7 +35064,11 @@
           <t>Repurchase of common shares 13(a)</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -38362,7 +38378,11 @@
           <t>Share-based compensation expense 12(b)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -61964,7 +61984,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E571" s="5" t="n">
         <v>-1.584</v>
       </c>
